--- a/outputs/webinar-gelaende/launch-auswertung-gelaende.xlsx
+++ b/outputs/webinar-gelaende/launch-auswertung-gelaende.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="101">
   <si>
     <t>Launch-Auswertung Gelände-Webinar</t>
   </si>
@@ -122,7 +122,22 @@
     <t>VERKAUF — PROGRAMM (549 €)</t>
   </si>
   <si>
-    <t>Programm-Käufe (Stück)</t>
+    <t>Programm-Käufe gesamt (Stück)</t>
+  </si>
+  <si>
+    <t>Programm Nettoumsatz gesamt (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  davon Ads — Stück</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  davon Ads — Nettoumsatz (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  davon organisch — Stück</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  davon organisch — Nettoumsatz (€)</t>
   </si>
   <si>
     <t xml:space="preserve">  davon Einmalzahlung</t>
@@ -143,9 +158,6 @@
     <t>Netto-Käufe Programm (Stück)</t>
   </si>
   <si>
-    <t>Programm Nettoumsatz (€)</t>
-  </si>
-  <si>
     <t>VERKAUF — VIP-PAKET (9 €)</t>
   </si>
   <si>
@@ -170,7 +182,13 @@
     <t>UMSATZ &amp; WIRTSCHAFTLICHKEIT</t>
   </si>
   <si>
-    <t>Gesamt-Nettoumsatz (Programm + VIP) (€)</t>
+    <t>Ad-Umsatz (Programm-Ads + VIP-Ads) (€)</t>
+  </si>
+  <si>
+    <t>Organisch-Umsatz (Programm-org + VIP-org) (€)</t>
+  </si>
+  <si>
+    <t>Gesamt-Nettoumsatz (€)</t>
   </si>
   <si>
     <t>Ø Bestellwert Programm (€)</t>
@@ -185,25 +203,28 @@
     <t>Conversion Pitch→Kauf (Programm)</t>
   </si>
   <si>
-    <t>ROAS (Gesamt-Netto / Ad-Spend)</t>
-  </si>
-  <si>
-    <t>Gewinn grob (Gesamt-Netto - Ad-Spend)</t>
-  </si>
-  <si>
-    <t>Cost per Sale Programm (€)</t>
-  </si>
-  <si>
-    <t>Legende: Weiße Felder = du trägst ein. Beige Felder = rechnen sich automatisch.</t>
-  </si>
-  <si>
-    <t>VIP-Split nach Devine-Tags (Ads 15 / organisch 21 = 36). Netto-Gesamt 269,94 € aus ThriveCart (35 bezahlte Charges), anteilig verteilt. Differenz von 1 = wohl Gutschein/Storno.</t>
-  </si>
-  <si>
-    <t>Programm-549-€-Käufe am Cart-Close (Do 27.08.) eintragen: Stückzahl + Programm Nettoumsatz. Dann rechnen sich ROAS, Gewinn und Conversions automatisch.</t>
-  </si>
-  <si>
-    <t>Ad-Spend + Lead-Kosten aus Meta/Tags. Opt-in-Aufrufe von Anika (org 318 / Ads 882). Salespage-Aufrufe noch nachtragen.</t>
+    <t>★ Ad-ROAS (nur Ads-Umsatz / Ad-Spend)</t>
+  </si>
+  <si>
+    <t>Gesamt-ROAS (Gesamt-Umsatz / Ad-Spend)</t>
+  </si>
+  <si>
+    <t>Cost per Ad-Sale (Ad-Spend / Ads-Käufe) (€)</t>
+  </si>
+  <si>
+    <t>Gewinn grob (Gesamt-Umsatz - Ad-Spend) (€)</t>
+  </si>
+  <si>
+    <t>Legende: Weiße Felder = du trägst ein. Beige Felder = rechnen sich automatisch. ★ Ad-ROAS = die wichtigste Ads-Kennzahl.</t>
+  </si>
+  <si>
+    <t>Stand Di 25.08.: 4 Programm-Käufe (3 Einmalzahlung + 1 Teilzahlung), Nettoumsatz 1.938,66 € (Teilzahlung als voller Vertragswert). VIP 36 / 269,94 €.</t>
+  </si>
+  <si>
+    <t>Ads/organisch-Split trägst du manuell nach (eine Salespage, keine automatische Trennung). Du siehst beim Kauf, wer aus Ads oder organisch kam, und füllst die weißen Ads-/organisch-Felder selbst.</t>
+  </si>
+  <si>
+    <t>Sobald die Ads-/organisch-Felder gefüllt sind, rechnet sich der Ad-ROAS (nur Ads-Umsatz gegen Ad-Spend) automatisch.</t>
   </si>
   <si>
     <t>Sales-Mail-Auswertung Gelände-Webinar (Aug 2026)</t>
@@ -784,10 +805,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="8" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1333,7 +1354,9 @@
       <c r="A32" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="8"/>
+      <c r="B32" s="8">
+        <v>5</v>
+      </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
@@ -1345,19 +1368,23 @@
       <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="B33" s="10">
+        <v>2400</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="8"/>
+      <c r="B34" s="8">
+        <v>2</v>
+      </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -1369,19 +1396,23 @@
       <c r="A35" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="B35" s="10">
+        <v>922.68</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="8"/>
+      <c r="B36" s="8">
+        <v>3</v>
+      </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -1393,71 +1424,61 @@
       <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
+      <c r="B37" s="10">
+        <v>1477.32</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="9">
-        <f>IF(B32="","",B32-IF(B37="",0,B37))</f>
-      </c>
-      <c r="C38" s="9">
-        <f>IF(C32="","",C32-IF(C37="",0,C37))</f>
-      </c>
-      <c r="D38" s="9">
-        <f>IF(D32="","",D32-IF(D37="",0,D37))</f>
-      </c>
-      <c r="E38" s="9">
-        <f>IF(E32="","",E32-IF(E37="",0,E37))</f>
-      </c>
-      <c r="F38" s="9">
-        <f>IF(F32="","",F32-IF(F37="",0,F37))</f>
-      </c>
-      <c r="G38" s="9">
-        <f>IF(G32="","",G32-IF(G37="",0,G37))</f>
-      </c>
-      <c r="H38" s="9">
-        <f>IF(H32="","",H32-IF(H37="",0,H37))</f>
-      </c>
+      <c r="B38" s="8">
+        <v>4</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
+      <c r="B39" s="8">
+        <v>1</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="8">
-        <v>15</v>
-      </c>
+      <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
@@ -1469,262 +1490,222 @@
       <c r="A42" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="10">
-        <v>112.48</v>
-      </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="8">
-        <v>21</v>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="B43" s="9">
+        <f>IF(B32="","",B32-IF(B42="",0,B42))</f>
+      </c>
+      <c r="C43" s="9">
+        <f>IF(C32="","",C32-IF(C42="",0,C42))</f>
+      </c>
+      <c r="D43" s="9">
+        <f>IF(D32="","",D32-IF(D42="",0,D42))</f>
+      </c>
+      <c r="E43" s="9">
+        <f>IF(E32="","",E32-IF(E42="",0,E42))</f>
+      </c>
+      <c r="F43" s="9">
+        <f>IF(F32="","",F32-IF(F42="",0,F42))</f>
+      </c>
+      <c r="G43" s="9">
+        <f>IF(G32="","",G32-IF(G42="",0,G42))</f>
+      </c>
+      <c r="H43" s="9">
+        <f>IF(H32="","",H32-IF(H42="",0,H42))</f>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="10">
-        <v>157.46</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="9">
-        <f>B41+B43</f>
-      </c>
-      <c r="C45" s="9">
-        <f>C41+C43</f>
-      </c>
-      <c r="D45" s="9">
-        <f>D41+D43</f>
-      </c>
-      <c r="E45" s="9">
-        <f>E41+E43</f>
-      </c>
-      <c r="F45" s="9">
-        <f>F41+F43</f>
-      </c>
-      <c r="G45" s="9">
-        <f>G41+G43</f>
-      </c>
-      <c r="H45" s="9">
-        <f>H41+H43</f>
-      </c>
+      <c r="B45" s="8">
+        <v>15</v>
+      </c>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="11">
-        <f>B42+B44</f>
-      </c>
-      <c r="C46" s="11">
-        <f>C42+C44</f>
-      </c>
-      <c r="D46" s="11">
-        <f>D42+D44</f>
-      </c>
-      <c r="E46" s="11">
-        <f>E42+E44</f>
-      </c>
-      <c r="F46" s="11">
-        <f>F42+F44</f>
-      </c>
-      <c r="G46" s="11">
-        <f>G42+G44</f>
-      </c>
-      <c r="H46" s="11">
-        <f>H42+H44</f>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="B46" s="10">
+        <v>112.48</v>
+      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
+      <c r="B47" s="8">
+        <v>21</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="11">
-        <f>N(B39)+N(B46)</f>
-      </c>
-      <c r="C48" s="11">
-        <f>N(C39)+N(C46)</f>
-      </c>
-      <c r="D48" s="11">
-        <f>N(D39)+N(D46)</f>
-      </c>
-      <c r="E48" s="11">
-        <f>N(E39)+N(E46)</f>
-      </c>
-      <c r="F48" s="11">
-        <f>N(F39)+N(F46)</f>
-      </c>
-      <c r="G48" s="11">
-        <f>N(G39)+N(G46)</f>
-      </c>
-      <c r="H48" s="11">
-        <f>N(H39)+N(H46)</f>
-      </c>
+      <c r="B48" s="10">
+        <v>157.46</v>
+      </c>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="11">
-        <f>IF(OR(B32="",B32=0),"",B39/B32)</f>
-      </c>
-      <c r="C49" s="11">
-        <f>IF(OR(C32="",C32=0),"",C39/C32)</f>
-      </c>
-      <c r="D49" s="11">
-        <f>IF(OR(D32="",D32=0),"",D39/D32)</f>
-      </c>
-      <c r="E49" s="11">
-        <f>IF(OR(E32="",E32=0),"",E39/E32)</f>
-      </c>
-      <c r="F49" s="11">
-        <f>IF(OR(F32="",F32=0),"",F39/F32)</f>
-      </c>
-      <c r="G49" s="11">
-        <f>IF(OR(G32="",G32=0),"",G39/G32)</f>
-      </c>
-      <c r="H49" s="11">
-        <f>IF(OR(H32="",H32=0),"",H39/H32)</f>
+      <c r="B49" s="9">
+        <f>B45+B47</f>
+      </c>
+      <c r="C49" s="9">
+        <f>C45+C47</f>
+      </c>
+      <c r="D49" s="9">
+        <f>D45+D47</f>
+      </c>
+      <c r="E49" s="9">
+        <f>E45+E47</f>
+      </c>
+      <c r="F49" s="9">
+        <f>F45+F47</f>
+      </c>
+      <c r="G49" s="9">
+        <f>G45+G47</f>
+      </c>
+      <c r="H49" s="9">
+        <f>H45+H47</f>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="12">
-        <f>IF(OR(B32="",B12=0),"",B32/B12)</f>
-      </c>
-      <c r="C50" s="12">
-        <f>IF(OR(C32="",C12=0),"",C32/C12)</f>
-      </c>
-      <c r="D50" s="12">
-        <f>IF(OR(D32="",D12=0),"",D32/D12)</f>
-      </c>
-      <c r="E50" s="12">
-        <f>IF(OR(E32="",E12=0),"",E32/E12)</f>
-      </c>
-      <c r="F50" s="12">
-        <f>IF(OR(F32="",F12=0),"",F32/F12)</f>
-      </c>
-      <c r="G50" s="12">
-        <f>IF(OR(G32="",G12=0),"",G32/G12)</f>
-      </c>
-      <c r="H50" s="12">
-        <f>IF(OR(H32="",H12=0),"",H32/H12)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="B50" s="11">
+        <f>B46+B48</f>
+      </c>
+      <c r="C50" s="11">
+        <f>C46+C48</f>
+      </c>
+      <c r="D50" s="11">
+        <f>D46+D48</f>
+      </c>
+      <c r="E50" s="11">
+        <f>E46+E48</f>
+      </c>
+      <c r="F50" s="11">
+        <f>F46+F48</f>
+      </c>
+      <c r="G50" s="11">
+        <f>G46+G48</f>
+      </c>
+      <c r="H50" s="11">
+        <f>H46+H48</f>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="12">
-        <f>IF(OR(B32="",B25=0),"",B32/B25)</f>
-      </c>
-      <c r="C51" s="12">
-        <f>IF(OR(C32="",C25=0),"",C32/C25)</f>
-      </c>
-      <c r="D51" s="12">
-        <f>IF(OR(D32="",D25=0),"",D32/D25)</f>
-      </c>
-      <c r="E51" s="12">
-        <f>IF(OR(E32="",E25=0),"",E32/E25)</f>
-      </c>
-      <c r="F51" s="12">
-        <f>IF(OR(F32="",F25=0),"",F32/F25)</f>
-      </c>
-      <c r="G51" s="12">
-        <f>IF(OR(G32="",G25=0),"",G32/G25)</f>
-      </c>
-      <c r="H51" s="12">
-        <f>IF(OR(H32="",H25=0),"",H32/H25)</f>
-      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="12">
-        <f>IF(OR(B32="",B28=0),"",B32/B28)</f>
-      </c>
-      <c r="C52" s="12">
-        <f>IF(OR(C32="",C28=0),"",C32/C28)</f>
-      </c>
-      <c r="D52" s="12">
-        <f>IF(OR(D32="",D28=0),"",D32/D28)</f>
-      </c>
-      <c r="E52" s="12">
-        <f>IF(OR(E32="",E28=0),"",E32/E28)</f>
-      </c>
-      <c r="F52" s="12">
-        <f>IF(OR(F32="",F28=0),"",F32/F28)</f>
-      </c>
-      <c r="G52" s="12">
-        <f>IF(OR(G32="",G28=0),"",G32/G28)</f>
-      </c>
-      <c r="H52" s="12">
-        <f>IF(OR(H32="",H28=0),"",H32/H28)</f>
+      <c r="B52" s="11">
+        <f>N(B35)+N(B46)</f>
+      </c>
+      <c r="C52" s="11">
+        <f>N(C35)+N(C46)</f>
+      </c>
+      <c r="D52" s="11">
+        <f>N(D35)+N(D46)</f>
+      </c>
+      <c r="E52" s="11">
+        <f>N(E35)+N(E46)</f>
+      </c>
+      <c r="F52" s="11">
+        <f>N(F35)+N(F46)</f>
+      </c>
+      <c r="G52" s="11">
+        <f>N(G35)+N(G46)</f>
+      </c>
+      <c r="H52" s="11">
+        <f>N(H35)+N(H46)</f>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="13">
-        <f>IF(OR(B39="",B13="",B13=0),"",B48/B13)</f>
-      </c>
-      <c r="C53" s="13">
-        <f>IF(OR(C39="",C13="",C13=0),"",C48/C13)</f>
-      </c>
-      <c r="D53" s="13">
-        <f>IF(OR(D39="",D13="",D13=0),"",D48/D13)</f>
-      </c>
-      <c r="E53" s="13">
-        <f>IF(OR(E39="",E13="",E13=0),"",E48/E13)</f>
-      </c>
-      <c r="F53" s="13">
-        <f>IF(OR(F39="",F13="",F13=0),"",F48/F13)</f>
-      </c>
-      <c r="G53" s="13">
-        <f>IF(OR(G39="",G13="",G13=0),"",G48/G13)</f>
-      </c>
-      <c r="H53" s="13">
-        <f>IF(OR(H39="",H13="",H13=0),"",H48/H13)</f>
+      <c r="B53" s="11">
+        <f>N(B37)+N(B48)</f>
+      </c>
+      <c r="C53" s="11">
+        <f>N(C37)+N(C48)</f>
+      </c>
+      <c r="D53" s="11">
+        <f>N(D37)+N(D48)</f>
+      </c>
+      <c r="E53" s="11">
+        <f>N(E37)+N(E48)</f>
+      </c>
+      <c r="F53" s="11">
+        <f>N(F37)+N(F48)</f>
+      </c>
+      <c r="G53" s="11">
+        <f>N(G37)+N(G48)</f>
+      </c>
+      <c r="H53" s="11">
+        <f>N(H37)+N(H48)</f>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -1732,25 +1713,25 @@
         <v>58</v>
       </c>
       <c r="B54" s="11">
-        <f>IF(OR(B39="",B13=""),"",B48-B13)</f>
+        <f>N(B33)+N(B50)</f>
       </c>
       <c r="C54" s="11">
-        <f>IF(OR(C39="",C13=""),"",C48-C13)</f>
+        <f>N(C33)+N(C50)</f>
       </c>
       <c r="D54" s="11">
-        <f>IF(OR(D39="",D13=""),"",D48-D13)</f>
+        <f>N(D33)+N(D50)</f>
       </c>
       <c r="E54" s="11">
-        <f>IF(OR(E39="",E13=""),"",E48-E13)</f>
+        <f>N(E33)+N(E50)</f>
       </c>
       <c r="F54" s="11">
-        <f>IF(OR(F39="",F13=""),"",F48-F13)</f>
+        <f>N(F33)+N(F50)</f>
       </c>
       <c r="G54" s="11">
-        <f>IF(OR(G39="",G13=""),"",G48-G13)</f>
+        <f>N(G33)+N(G50)</f>
       </c>
       <c r="H54" s="11">
-        <f>IF(OR(H39="",H13=""),"",H48-H13)</f>
+        <f>N(H33)+N(H50)</f>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -1758,74 +1739,256 @@
         <v>59</v>
       </c>
       <c r="B55" s="11">
-        <f>IF(OR(B13="",B32="",B32=0),"",B13/B32)</f>
+        <f>IF(OR(B32="",B32=0),"",B33/B32)</f>
       </c>
       <c r="C55" s="11">
-        <f>IF(OR(C13="",C32="",C32=0),"",C13/C32)</f>
+        <f>IF(OR(C32="",C32=0),"",C33/C32)</f>
       </c>
       <c r="D55" s="11">
-        <f>IF(OR(D13="",D32="",D32=0),"",D13/D32)</f>
+        <f>IF(OR(D32="",D32=0),"",D33/D32)</f>
       </c>
       <c r="E55" s="11">
-        <f>IF(OR(E13="",E32="",E32=0),"",E13/E32)</f>
+        <f>IF(OR(E32="",E32=0),"",E33/E32)</f>
       </c>
       <c r="F55" s="11">
-        <f>IF(OR(F13="",F32="",F32=0),"",F13/F32)</f>
+        <f>IF(OR(F32="",F32=0),"",F33/F32)</f>
       </c>
       <c r="G55" s="11">
-        <f>IF(OR(G13="",G32="",G32=0),"",G13/G32)</f>
+        <f>IF(OR(G32="",G32=0),"",G33/G32)</f>
       </c>
       <c r="H55" s="11">
-        <f>IF(OR(H13="",H32="",H32=0),"",H13/H32)</f>
+        <f>IF(OR(H32="",H32=0),"",H33/H32)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="12">
+        <f>IF(OR(B32="",B12=0),"",B32/B12)</f>
+      </c>
+      <c r="C56" s="12">
+        <f>IF(OR(C32="",C12=0),"",C32/C12)</f>
+      </c>
+      <c r="D56" s="12">
+        <f>IF(OR(D32="",D12=0),"",D32/D12)</f>
+      </c>
+      <c r="E56" s="12">
+        <f>IF(OR(E32="",E12=0),"",E32/E12)</f>
+      </c>
+      <c r="F56" s="12">
+        <f>IF(OR(F32="",F12=0),"",F32/F12)</f>
+      </c>
+      <c r="G56" s="12">
+        <f>IF(OR(G32="",G12=0),"",G32/G12)</f>
+      </c>
+      <c r="H56" s="12">
+        <f>IF(OR(H32="",H12=0),"",H32/H12)</f>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
+      <c r="A57" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="12">
+        <f>IF(OR(B32="",B25=0),"",B32/B25)</f>
+      </c>
+      <c r="C57" s="12">
+        <f>IF(OR(C32="",C25=0),"",C32/C25)</f>
+      </c>
+      <c r="D57" s="12">
+        <f>IF(OR(D32="",D25=0),"",D32/D25)</f>
+      </c>
+      <c r="E57" s="12">
+        <f>IF(OR(E32="",E25=0),"",E32/E25)</f>
+      </c>
+      <c r="F57" s="12">
+        <f>IF(OR(F32="",F25=0),"",F32/F25)</f>
+      </c>
+      <c r="G57" s="12">
+        <f>IF(OR(G32="",G25=0),"",G32/G25)</f>
+      </c>
+      <c r="H57" s="12">
+        <f>IF(OR(H32="",H25=0),"",H32/H25)</f>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
+      <c r="A58" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="12">
+        <f>IF(OR(B32="",B28=0),"",B32/B28)</f>
+      </c>
+      <c r="C58" s="12">
+        <f>IF(OR(C32="",C28=0),"",C32/C28)</f>
+      </c>
+      <c r="D58" s="12">
+        <f>IF(OR(D32="",D28=0),"",D32/D28)</f>
+      </c>
+      <c r="E58" s="12">
+        <f>IF(OR(E32="",E28=0),"",E32/E28)</f>
+      </c>
+      <c r="F58" s="12">
+        <f>IF(OR(F32="",F28=0),"",F32/F28)</f>
+      </c>
+      <c r="G58" s="12">
+        <f>IF(OR(G32="",G28=0),"",G32/G28)</f>
+      </c>
+      <c r="H58" s="12">
+        <f>IF(OR(H32="",H28=0),"",H32/H28)</f>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
+      <c r="A59" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="13">
+        <f>IF(OR(B34="",B13="",B13=0),"",B52/B13)</f>
+      </c>
+      <c r="C59" s="13">
+        <f>IF(OR(C34="",C13="",C13=0),"",C52/C13)</f>
+      </c>
+      <c r="D59" s="13">
+        <f>IF(OR(D34="",D13="",D13=0),"",D52/D13)</f>
+      </c>
+      <c r="E59" s="13">
+        <f>IF(OR(E34="",E13="",E13=0),"",E52/E13)</f>
+      </c>
+      <c r="F59" s="13">
+        <f>IF(OR(F34="",F13="",F13=0),"",F52/F13)</f>
+      </c>
+      <c r="G59" s="13">
+        <f>IF(OR(G34="",G13="",G13=0),"",G52/G13)</f>
+      </c>
+      <c r="H59" s="13">
+        <f>IF(OR(H34="",H13="",H13=0),"",H52/H13)</f>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
+      <c r="A60" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="13">
+        <f>IF(OR(B33="",B13="",B13=0),"",B54/B13)</f>
+      </c>
+      <c r="C60" s="13">
+        <f>IF(OR(C33="",C13="",C13=0),"",C54/C13)</f>
+      </c>
+      <c r="D60" s="13">
+        <f>IF(OR(D33="",D13="",D13=0),"",D54/D13)</f>
+      </c>
+      <c r="E60" s="13">
+        <f>IF(OR(E33="",E13="",E13=0),"",E54/E13)</f>
+      </c>
+      <c r="F60" s="13">
+        <f>IF(OR(F33="",F13="",F13=0),"",F54/F13)</f>
+      </c>
+      <c r="G60" s="13">
+        <f>IF(OR(G33="",G13="",G13=0),"",G54/G13)</f>
+      </c>
+      <c r="H60" s="13">
+        <f>IF(OR(H33="",H13="",H13=0),"",H54/H13)</f>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="11">
+        <f>IF(OR(B34="",B34=0,B13=""),"",B13/B34)</f>
+      </c>
+      <c r="C61" s="11">
+        <f>IF(OR(C34="",C34=0,C13=""),"",C13/C34)</f>
+      </c>
+      <c r="D61" s="11">
+        <f>IF(OR(D34="",D34=0,D13=""),"",D13/D34)</f>
+      </c>
+      <c r="E61" s="11">
+        <f>IF(OR(E34="",E34=0,E13=""),"",E13/E34)</f>
+      </c>
+      <c r="F61" s="11">
+        <f>IF(OR(F34="",F34=0,F13=""),"",F13/F34)</f>
+      </c>
+      <c r="G61" s="11">
+        <f>IF(OR(G34="",G34=0,G13=""),"",G13/G34)</f>
+      </c>
+      <c r="H61" s="11">
+        <f>IF(OR(H34="",H34=0,H13=""),"",H13/H34)</f>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="11">
+        <f>IF(OR(B33="",B13=""),"",B54-B13)</f>
+      </c>
+      <c r="C62" s="11">
+        <f>IF(OR(C33="",C13=""),"",C54-C13)</f>
+      </c>
+      <c r="D62" s="11">
+        <f>IF(OR(D33="",D13=""),"",D54-D13)</f>
+      </c>
+      <c r="E62" s="11">
+        <f>IF(OR(E33="",E13=""),"",E54-E13)</f>
+      </c>
+      <c r="F62" s="11">
+        <f>IF(OR(F33="",F13=""),"",F54-F13)</f>
+      </c>
+      <c r="G62" s="11">
+        <f>IF(OR(G33="",G13=""),"",G54-G13)</f>
+      </c>
+      <c r="H62" s="11">
+        <f>IF(OR(H33="",H13=""),"",H54-H13)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1836,12 +1999,12 @@
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1861,7 +2024,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1874,7 +2037,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1887,42 +2050,42 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -1937,13 +2100,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -1958,13 +2121,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -1979,13 +2142,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -2000,13 +2163,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -2021,13 +2184,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2042,13 +2205,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>

--- a/outputs/webinar-gelaende/launch-auswertung-gelaende.xlsx
+++ b/outputs/webinar-gelaende/launch-auswertung-gelaende.xlsx
@@ -218,7 +218,7 @@
     <t>Legende: Weiße Felder = du trägst ein. Beige Felder = rechnen sich automatisch. ★ Ad-ROAS = die wichtigste Ads-Kennzahl.</t>
   </si>
   <si>
-    <t>Stand Di 25.08.: 4 Programm-Käufe (3 Einmalzahlung + 1 Teilzahlung), Nettoumsatz 1.938,66 € (Teilzahlung als voller Vertragswert). VIP 36 / 269,94 €.</t>
+    <t>Stand Mi 26.08.: 4 Programm-Käufe netto (3 Einmalzahlung + 1 Teilzahlung), Nettoumsatz 1.938,66 € (Teilzahlung als voller Vertragswert). Brutto waren es 5, 1 organische Einmalzahlung wurde storniert (−461,34 €) und ist hier bereits herausgerechnet. VIP 36 / 269,94 €.</t>
   </si>
   <si>
     <t>Ads/organisch-Split trägst du manuell nach (eine Salespage, keine automatische Trennung). Du siehst beim Kauf, wer aus Ads oder organisch kam, und füllst die weißen Ads-/organisch-Felder selbst.</t>
@@ -1355,7 +1355,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -1369,7 +1369,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="10">
-        <v>2400</v>
+        <v>1938.66</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -1411,7 +1411,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -1425,7 +1425,7 @@
         <v>41</v>
       </c>
       <c r="B37" s="10">
-        <v>1477.32</v>
+        <v>1015.98</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -1439,7 +1439,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>

--- a/outputs/webinar-gelaende/launch-auswertung-gelaende.xlsx
+++ b/outputs/webinar-gelaende/launch-auswertung-gelaende.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="116">
   <si>
     <t>Launch-Auswertung Gelände-Webinar</t>
   </si>
@@ -215,10 +215,40 @@
     <t>Gewinn grob (Gesamt-Umsatz - Ad-Spend) (€)</t>
   </si>
   <si>
+    <t>SHOW-UP NACH QUELLE (Proxy: Zoom-Link geklickt)</t>
+  </si>
+  <si>
+    <t>Zoom-Link-Klicker organisch (Stück)</t>
+  </si>
+  <si>
+    <t>Zoom-Link-Klicker Ads (Stück)</t>
+  </si>
+  <si>
+    <t>Show-up organisch (Proxy)</t>
+  </si>
+  <si>
+    <t>Show-up Ads (Proxy)</t>
+  </si>
+  <si>
+    <t>ADS-KÄUFERINNEN — ANMELDEDATUM (fürs Ads-Timing)</t>
+  </si>
+  <si>
+    <t>Ads-Käuferin 1 angemeldet am</t>
+  </si>
+  <si>
+    <t>10.08.2026 (13 Tage vor Webinar)</t>
+  </si>
+  <si>
+    <t>Ads-Käuferin 2 angemeldet am</t>
+  </si>
+  <si>
+    <t>22.08.2026 (1 Tag vor Webinar)</t>
+  </si>
+  <si>
     <t>Legende: Weiße Felder = du trägst ein. Beige Felder = rechnen sich automatisch. ★ Ad-ROAS = die wichtigste Ads-Kennzahl.</t>
   </si>
   <si>
-    <t>Stand Mi 26.08.: 4 Programm-Käufe netto (3 Einmalzahlung + 1 Teilzahlung), Nettoumsatz 1.938,66 € (Teilzahlung als voller Vertragswert). Brutto waren es 5, 1 organische Einmalzahlung wurde storniert (−461,34 €) und ist hier bereits herausgerechnet. VIP 36 / 269,94 €.</t>
+    <t>ENDSTAND (Verkaufsphase beendet, Do 27.08.): 7 Programm-Käufe netto (5 Einmalzahlung + 2 Teilzahlung), Nettoumsatz 3.415,98 € (Teilzahlung als voller Vertragswert). 1 organische Einmalzahlung wurde storniert (−461,34 €) und ist bereits herausgerechnet. Aufteilung: Ads 2 / 922,68 €, organisch 5 / 2.493,30 €. Mindestens 1 Verkauf kam über ein Gespräch. VIP 36 / 269,94 €. Gesamt-Nettoumsatz 3.685,92 €, Ad-Spend 1.124,64 €, Gewinn grob 2.561,28 €.</t>
   </si>
   <si>
     <t>Ads/organisch-Split trägst du manuell nach (eine Salespage, keine automatische Trennung). Du siehst beim Kauf, wer aus Ads oder organisch kam, und füllst die weißen Ads-/organisch-Felder selbst.</t>
@@ -227,10 +257,13 @@
     <t>Sobald die Ads-/organisch-Felder gefüllt sind, rechnet sich der Ad-ROAS (nur Ads-Umsatz gegen Ad-Spend) automatisch.</t>
   </si>
   <si>
+    <t>Show-up nach Quelle = Näherung über „Zoom-Link geklickt" (4 Erinnerungs-/Live-Mails, dedupliziert, gegen die Anmeldelisten gematcht; Bot-/Scanner-Klicks fallen automatisch raus). Klick ist etwas lockerer als „bis zum Schluss dabei". Verifiziert plausibel: Proxy-Gesamt 42,9 % liegt knapp über der echten Gesamt-Show-up von 40,5 %.</t>
+  </si>
+  <si>
     <t>Sales-Mail-Auswertung Gelände-Webinar (Aug 2026)</t>
   </si>
   <si>
-    <t>Öffnungs-/Klickraten aus Devine nachtragen. „Käufe danach" = Verkäufe, die zeitlich auf diese Mail folgten.</t>
+    <t>Zahlen aus Devine (Zugestellt/Geöffnet/Geklickt/Abmeldung). Öffnungs- und Klickrate rechnen sich automatisch. „Käufe danach" = Verkäufe, die zeitlich auf diese Mail folgten.</t>
   </si>
   <si>
     <t>Mail</t>
@@ -257,10 +290,13 @@
     <t>Klickrate</t>
   </si>
   <si>
+    <t>Abmeldungen</t>
+  </si>
+  <si>
     <t>Käufe danach</t>
   </si>
   <si>
-    <t>Mail 1 Schnellentschlossene</t>
+    <t>Mail 1 direkt nach Webinar</t>
   </si>
   <si>
     <t>🐴 Für die Schnellentschlossenen unter euch</t>
@@ -278,13 +314,13 @@
     <t>Mo 24.08.</t>
   </si>
   <si>
-    <t>Mail 3 Frühbucher-Deadline</t>
+    <t>Mail 3 Frühbucher Ende</t>
   </si>
   <si>
     <t>⏳ Um Mitternacht ist der Schmerzguide weg</t>
   </si>
   <si>
-    <t>Mail 4 Programm-Details</t>
+    <t>Mail 4 Kursinhalte</t>
   </si>
   <si>
     <t>🐴 Alles, was im Gelände-Programm auf dich wartet</t>
@@ -293,7 +329,7 @@
     <t>Di 25.08.</t>
   </si>
   <si>
-    <t>Mail 5 FAQ + Garantie</t>
+    <t>Mail 5 FAQ</t>
   </si>
   <si>
     <t>Dein Name fehlt noch auf meiner Liste</t>
@@ -302,7 +338,7 @@
     <t>Mi 26.08.</t>
   </si>
   <si>
-    <t>Mail 6 Zweifel + Testimonials</t>
+    <t>Mail 6 Einwand</t>
   </si>
   <si>
     <t>Schaffe ich das wirklich alleine?</t>
@@ -311,10 +347,19 @@
     <t>Do 27.08.</t>
   </si>
   <si>
-    <t>Mail 7 Last Call</t>
+    <t>Mail 7 Ende</t>
   </si>
   <si>
     <t>⏳ Gleich ist die Tür zu</t>
+  </si>
+  <si>
+    <t>Abmeldungen gesamt (Sequenz)</t>
+  </si>
+  <si>
+    <t>Soft-Opt-out genutzt (Trigger-Link, nur aus Sales-Strecke raus)</t>
+  </si>
+  <si>
+    <t>Der Soft-Opt-out sind Kontakte, die keine weiteren Sales-Mails wollten, aber über den Trigger-Link auf der Liste geblieben sind (statt komplett abzumelden). Quelle: Anmeldeverlauf des Workflows „Gelände Sales Opt-out".</t>
   </si>
 </sst>
 </file>
@@ -325,7 +370,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -376,6 +421,13 @@
       <i/>
       <color rgb="FF7A6050"/>
     </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF7B3F28"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -417,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -464,6 +516,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -805,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1355,7 +1414,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -1369,7 +1428,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="10">
-        <v>1938.66</v>
+        <v>3415.98</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -1411,7 +1470,7 @@
         <v>40</v>
       </c>
       <c r="B36" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -1425,7 +1484,7 @@
         <v>41</v>
       </c>
       <c r="B37" s="10">
-        <v>1015.98</v>
+        <v>2493.3</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -1439,7 +1498,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -1453,7 +1512,7 @@
         <v>43</v>
       </c>
       <c r="B39" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -1466,7 +1525,9 @@
       <c r="A40" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="8"/>
+      <c r="B40" s="8">
+        <v>4</v>
+      </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
@@ -1478,7 +1539,9 @@
       <c r="A41" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="8"/>
+      <c r="B41" s="8">
+        <v>4</v>
+      </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
@@ -1942,56 +2005,200 @@
         <f>IF(OR(H33="",H13=""),"",H54-H13)</f>
       </c>
     </row>
+    <row r="63" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+    </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
+      <c r="A64" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="8">
+        <v>81</v>
+      </c>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
+      <c r="A65" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="8">
+        <v>72</v>
+      </c>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
+      <c r="A66" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="12">
+        <f>IF(OR(B64="",B9=0),"",B64/B9)</f>
+      </c>
+      <c r="C66" s="12">
+        <f>IF(OR(C64="",C9=0),"",C64/C9)</f>
+      </c>
+      <c r="D66" s="12">
+        <f>IF(OR(D64="",D9=0),"",D64/D9)</f>
+      </c>
+      <c r="E66" s="12">
+        <f>IF(OR(E64="",E9=0),"",E64/E9)</f>
+      </c>
+      <c r="F66" s="12">
+        <f>IF(OR(F64="",F9=0),"",F64/F9)</f>
+      </c>
+      <c r="G66" s="12">
+        <f>IF(OR(G64="",G9=0),"",G64/G9)</f>
+      </c>
+      <c r="H66" s="12">
+        <f>IF(OR(H64="",H9=0),"",H64/H9)</f>
+      </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
+      <c r="A67" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="12">
+        <f>IF(OR(B65="",B10=0),"",B65/B10)</f>
+      </c>
+      <c r="C67" s="12">
+        <f>IF(OR(C65="",C10=0),"",C65/C10)</f>
+      </c>
+      <c r="D67" s="12">
+        <f>IF(OR(D65="",D10=0),"",D65/D10)</f>
+      </c>
+      <c r="E67" s="12">
+        <f>IF(OR(E65="",E10=0),"",E65/E10)</f>
+      </c>
+      <c r="F67" s="12">
+        <f>IF(OR(F65="",F10=0),"",F65/F10)</f>
+      </c>
+      <c r="G67" s="12">
+        <f>IF(OR(G65="",G10=0),"",G65/G10)</f>
+      </c>
+      <c r="H67" s="12">
+        <f>IF(OR(H65="",H10=0),"",H65/H10)</f>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -2001,10 +2208,13 @@
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A76:H76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2013,18 +2223,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="9" width="13" customWidth="1"/>
+    <col min="4" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2034,10 +2244,11 @@
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
       <c r="I1" s="15"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="15"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2047,187 +2258,285 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+        <v>96</v>
+      </c>
+      <c r="D4" s="8">
+        <v>332</v>
+      </c>
+      <c r="E4" s="8">
+        <v>202</v>
+      </c>
       <c r="F4" s="19">
         <f>IF(OR(D4="",D4=0),"",E4/D4)</f>
       </c>
-      <c r="G4" s="8"/>
+      <c r="G4" s="8">
+        <v>36</v>
+      </c>
       <c r="H4" s="19">
         <f>IF(OR(D4="",D4=0),"",G4/D4)</f>
       </c>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4" s="8">
+        <v>4</v>
+      </c>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+        <v>99</v>
+      </c>
+      <c r="D5" s="8">
+        <v>327</v>
+      </c>
+      <c r="E5" s="8">
+        <v>157</v>
+      </c>
       <c r="F5" s="19">
         <f>IF(OR(D5="",D5=0),"",E5/D5)</f>
       </c>
-      <c r="G5" s="8"/>
+      <c r="G5" s="8">
+        <v>12</v>
+      </c>
       <c r="H5" s="19">
         <f>IF(OR(D5="",D5=0),"",G5/D5)</f>
       </c>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="8">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+        <v>99</v>
+      </c>
+      <c r="D6" s="8">
+        <v>314</v>
+      </c>
+      <c r="E6" s="8">
+        <v>138</v>
+      </c>
       <c r="F6" s="19">
         <f>IF(OR(D6="",D6=0),"",E6/D6)</f>
       </c>
-      <c r="G6" s="8"/>
+      <c r="G6" s="8">
+        <v>13</v>
+      </c>
       <c r="H6" s="19">
         <f>IF(OR(D6="",D6=0),"",G6/D6)</f>
       </c>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="8">
+        <v>3</v>
+      </c>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+        <v>104</v>
+      </c>
+      <c r="D7" s="8">
+        <v>306</v>
+      </c>
+      <c r="E7" s="8">
+        <v>140</v>
+      </c>
       <c r="F7" s="19">
         <f>IF(OR(D7="",D7=0),"",E7/D7)</f>
       </c>
-      <c r="G7" s="8"/>
+      <c r="G7" s="8">
+        <v>6</v>
+      </c>
       <c r="H7" s="19">
         <f>IF(OR(D7="",D7=0),"",G7/D7)</f>
       </c>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" s="8">
+        <v>5</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+        <v>107</v>
+      </c>
+      <c r="D8" s="8">
+        <v>302</v>
+      </c>
+      <c r="E8" s="8">
+        <v>144</v>
+      </c>
       <c r="F8" s="19">
         <f>IF(OR(D8="",D8=0),"",E8/D8)</f>
       </c>
-      <c r="G8" s="8"/>
+      <c r="G8" s="8">
+        <v>10</v>
+      </c>
       <c r="H8" s="19">
         <f>IF(OR(D8="",D8=0),"",G8/D8)</f>
       </c>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" s="8">
+        <v>3</v>
+      </c>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="8">
+        <v>295</v>
+      </c>
+      <c r="E9" s="8">
         <v>97</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
       <c r="F9" s="19">
         <f>IF(OR(D9="",D9=0),"",E9/D9)</f>
       </c>
-      <c r="G9" s="8"/>
+      <c r="G9" s="8">
+        <v>5</v>
+      </c>
       <c r="H9" s="19">
         <f>IF(OR(D9="",D9=0),"",G9/D9)</f>
       </c>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+        <v>110</v>
+      </c>
+      <c r="D10" s="8">
+        <v>294</v>
+      </c>
+      <c r="E10" s="8">
+        <v>86</v>
+      </c>
       <c r="F10" s="19">
         <f>IF(OR(D10="",D10=0),"",E10/D10)</f>
       </c>
-      <c r="G10" s="8"/>
+      <c r="G10" s="8">
+        <v>7</v>
+      </c>
       <c r="H10" s="19">
         <f>IF(OR(D10="",D10=0),"",G10/D10)</f>
       </c>
-      <c r="I10" s="8"/>
+      <c r="I10" s="8">
+        <v>2</v>
+      </c>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="20">
+        <f>SUM(I4:I10)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="I13" s="22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A14:J14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
